--- a/business_forms/033_mitigation_bank_reservation_form--business_forms.xlsx
+++ b/business_forms/033_mitigation_bank_reservation_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1488,29 +1488,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>chatjimmy</t>
+          <t>chat_jimmy</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>chatjimmy</t>
+          <t>chat jimmy</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>reserved_by_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>chat_jimmy</t>
+          <t>consultant</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>chat_jimmy</t>
+          <t>Consultant</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>consultant</t>
+          <t>developer</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Consultant</t>
+          <t>Developer</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>developer</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Developer</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1556,29 +1556,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>reserved_by_choices</t>
+          <t>assigned_to_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
@@ -1590,19 +1590,19 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>chatjimmy</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>chatjimmy</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>assigned_to_choices</t>
+          <t>created_by_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1624,46 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>chatjimmy</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>chatjimmy</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>created_by_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>chatjimmy</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>chatjimmy</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>created_by_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>chatjimmy</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>chatjimmy</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
